--- a/tabtools/demo/demo_stratetab.xlsx
+++ b/tabtools/demo/demo_stratetab.xlsx
@@ -72,16 +72,16 @@
     <t>Per 1,000 PY (95% CI)</t>
   </si>
   <si>
-    <t>6.3 (5.5-7.3)</t>
+    <t>6.3 (5.5, 7.3)</t>
   </si>
   <si>
-    <t>7.2 (6.2-8.4)</t>
+    <t>7.2 (6.2, 8.4)</t>
   </si>
   <si>
-    <t>5.5 (4.6-6.5)</t>
+    <t>5.5 (4.6, 6.5)</t>
   </si>
   <si>
-    <t>6.6 (5.5-7.8)</t>
+    <t>6.6 (5.5, 7.8)</t>
   </si>
   <si>
     <t>IRR (95% CI)</t>
@@ -90,10 +90,10 @@
     <t>Ref.</t>
   </si>
   <si>
-    <t>0.87 (0.69-1.09)</t>
+    <t>0.87 (0.69, 1.09)</t>
   </si>
   <si>
-    <t>0.91 (0.72-1.15)</t>
+    <t>0.91 (0.72, 1.15)</t>
   </si>
   <si>
     <t>Self-Harm</t>
@@ -111,22 +111,22 @@
     <t>36</t>
   </si>
   <si>
-    <t>1.9 (1.4-2.4)</t>
+    <t>1.9 (1.4, 2.4)</t>
   </si>
   <si>
-    <t>2.6 (2.0-3.4)</t>
+    <t>2.6 (2.0, 3.4)</t>
   </si>
   <si>
-    <t>1.4 (1.0-2.0)</t>
+    <t>1.4 (1.0, 2.0)</t>
   </si>
   <si>
-    <t>1.8 (1.3-2.6)</t>
+    <t>1.8 (1.3, 2.6)</t>
   </si>
   <si>
-    <t>0.78 (0.51-1.19)</t>
+    <t>0.78 (0.51, 1.19)</t>
   </si>
   <si>
-    <t>0.71 (0.47-1.07)</t>
+    <t>0.71 (0.47, 1.07)</t>
   </si>
   <si>
     <t>IRR = incidence rate ratio, Female vs Male. CI by log-normal method.</t>
